--- a/etsy-templates/Trip-Planner.xlsx
+++ b/etsy-templates/Trip-Planner.xlsx
@@ -385,7 +385,7 @@
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd\ mmm\ yyyy"/>
-    <numFmt numFmtId="166" formatCode="\$#,##0.00;&quot;-$&quot;#,##0.00;\-"/>
+    <numFmt numFmtId="166" formatCode="\£#,##0.00;&quot;-£&quot;#,##0.00;\-"/>
     <numFmt numFmtId="167" formatCode="0"/>
     <numFmt numFmtId="168" formatCode="0%"/>
     <numFmt numFmtId="169" formatCode="ddd\ dd\ mmm"/>
@@ -1190,7 +1190,7 @@
             <c:numRef>
               <c:f>Budget!$D$6:$D$13</c:f>
               <c:numCache>
-                <c:formatCode>\$#,##0.00;"-$"#,##0.00;\-</c:formatCode>
+                <c:formatCode>\£#,##0.00;"-£"#,##0.00;\-</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>420</c:v>
@@ -1771,7 +1771,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C49DCFE6-D640-4310-A8DE-3710509C22A4}</x14:id>
+          <x14:id>{5E82E3F4-B0A7-4989-9A6B-85868CF59A12}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -1787,7 +1787,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C49DCFE6-D640-4310-A8DE-3710509C22A4}">
+          <x14:cfRule type="dataBar" id="{5E82E3F4-B0A7-4989-9A6B-85868CF59A12}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -5958,7 +5958,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{62662191-FCFC-4FD9-B133-6533DFDE3C7F}</x14:id>
+          <x14:id>{00D87996-D098-40EB-A0E8-AC9EA3855674}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5985,7 +5985,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{62662191-FCFC-4FD9-B133-6533DFDE3C7F}">
+          <x14:cfRule type="dataBar" id="{00D87996-D098-40EB-A0E8-AC9EA3855674}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
